--- a/assets/data/generatordata.xlsx
+++ b/assets/data/generatordata.xlsx
@@ -28105,7 +28105,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A88DAEB-E71A-418F-A6F0-324150077FCF}">
-  <dimension ref="A1:L231"/>
+  <dimension ref="A1:M231"/>
   <sheetFormatPr defaultColWidth="80" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -28122,7 +28122,7 @@
     <col min="12" max="12" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -28158,6 +28158,11 @@
       </c>
       <c r="L1" s="1" t="s">
         <v>1047</v>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>required_deity</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -31116,7 +31121,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>2231</v>
       </c>
@@ -31141,6 +31146,11 @@
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>Zon-Kuthon</t>
+        </is>
+      </c>
     </row>
     <row r="134" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">

--- a/assets/data/generatordata.xlsx
+++ b/assets/data/generatordata.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9506" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9501" uniqueCount="2232">
   <si>
     <t>ancestry</t>
   </si>
@@ -34153,7 +34153,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2717403-A86F-4CD6-B8C6-9D0D28D17D33}">
-  <dimension ref="A1:E486"/>
+  <dimension ref="A1:E485"/>
   <sheetFormatPr defaultColWidth="76.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" customWidth="1"/>
@@ -34488,16 +34488,16 @@
     </row>
     <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>1331</v>
+        <v>2174</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1333</v>
+        <v>2203</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>420</v>
@@ -34505,16 +34505,16 @@
     </row>
     <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>2174</v>
+        <v>1334</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1309</v>
+        <v>1336</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>2203</v>
+        <v>848</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>420</v>
@@ -34522,13 +34522,13 @@
     </row>
     <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1336</v>
+        <v>1314</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>848</v>
@@ -34539,13 +34539,13 @@
     </row>
     <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1314</v>
+        <v>1339</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>848</v>
@@ -34556,13 +34556,13 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1339</v>
+        <v>1298</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>848</v>
@@ -34573,13 +34573,13 @@
     </row>
     <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1298</v>
+        <v>1342</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>848</v>
@@ -34590,13 +34590,13 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>848</v>
@@ -34607,13 +34607,13 @@
     </row>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1336</v>
+        <v>1307</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>848</v>
@@ -34624,16 +34624,16 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>848</v>
+        <v>1346</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>420</v>
@@ -34641,30 +34641,28 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1335</v>
+        <v>1348</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1300</v>
+        <v>1314</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1346</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1314</v>
+        <v>1305</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>848</v>
@@ -34673,13 +34671,13 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1305</v>
+        <v>1324</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>848</v>
@@ -34688,13 +34686,13 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1324</v>
+        <v>1309</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>848</v>
@@ -34703,13 +34701,13 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>848</v>
@@ -34718,13 +34716,13 @@
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>848</v>
@@ -34733,13 +34731,13 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>848</v>
@@ -34748,45 +34746,45 @@
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>1354</v>
+        <v>2225</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1326</v>
+        <v>1371</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="E38" s="2"/>
+        <v>2203</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>2225</v>
+        <v>1355</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1371</v>
+        <v>1356</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>2203</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>848</v>
@@ -34795,45 +34793,45 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="E41" s="2"/>
+        <v>982</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1318</v>
+        <v>1361</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>1348</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1361</v>
+        <v>1307</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>848</v>
@@ -34842,28 +34840,30 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1348</v>
+        <v>1364</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1307</v>
+        <v>1365</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>848</v>
@@ -34874,13 +34874,13 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1367</v>
+        <v>1318</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>848</v>
@@ -34891,13 +34891,13 @@
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1318</v>
+        <v>1293</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>848</v>
@@ -34908,13 +34908,13 @@
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1293</v>
+        <v>1371</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>848</v>
@@ -34925,13 +34925,13 @@
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>848</v>
@@ -34942,13 +34942,13 @@
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1373</v>
+        <v>1330</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>848</v>
@@ -34959,13 +34959,13 @@
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1330</v>
+        <v>1376</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>848</v>
@@ -34976,13 +34976,13 @@
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>1364</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1376</v>
+        <v>1339</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>848</v>
@@ -34993,13 +34993,13 @@
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1364</v>
+        <v>1379</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1339</v>
+        <v>1318</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>848</v>
@@ -35010,13 +35010,13 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1318</v>
+        <v>1381</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>848</v>
@@ -35027,13 +35027,13 @@
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1381</v>
+        <v>1309</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>848</v>
@@ -35044,13 +35044,13 @@
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>848</v>
@@ -35061,13 +35061,13 @@
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1305</v>
+        <v>1385</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>848</v>
@@ -35078,13 +35078,13 @@
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>848</v>
@@ -35095,13 +35095,13 @@
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>848</v>
@@ -35112,13 +35112,13 @@
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1389</v>
+        <v>1318</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>848</v>
@@ -35129,13 +35129,13 @@
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1318</v>
+        <v>1392</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>848</v>
@@ -35146,13 +35146,13 @@
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1392</v>
+        <v>1314</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>848</v>
@@ -35163,13 +35163,13 @@
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>1393</v>
+        <v>1331</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>848</v>
@@ -35180,13 +35180,13 @@
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>1331</v>
+        <v>1394</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1303</v>
+        <v>1395</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>848</v>
@@ -35197,13 +35197,13 @@
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1395</v>
+        <v>1381</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>848</v>
@@ -35214,13 +35214,13 @@
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1381</v>
+        <v>1336</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>848</v>
@@ -35231,13 +35231,13 @@
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1336</v>
+        <v>1387</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>848</v>
@@ -35248,13 +35248,13 @@
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1387</v>
+        <v>1400</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>848</v>
@@ -35265,13 +35265,13 @@
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>848</v>
@@ -35282,13 +35282,13 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>1379</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1402</v>
+        <v>1318</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>848</v>
@@ -35299,13 +35299,13 @@
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1379</v>
+        <v>1405</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1318</v>
+        <v>1300</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>848</v>
@@ -35316,13 +35316,13 @@
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1300</v>
+        <v>1407</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>848</v>
@@ -35333,13 +35333,13 @@
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>848</v>
@@ -35350,13 +35350,13 @@
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1402</v>
+        <v>1324</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>848</v>
@@ -35367,13 +35367,13 @@
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>848</v>
@@ -35384,13 +35384,13 @@
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1322</v>
+        <v>1307</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>848</v>
@@ -35401,13 +35401,13 @@
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>848</v>
@@ -35418,13 +35418,13 @@
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1300</v>
+        <v>1414</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>848</v>
@@ -35435,13 +35435,13 @@
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>1414</v>
+        <v>1322</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>848</v>
@@ -35452,13 +35452,13 @@
     </row>
     <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>1322</v>
+        <v>1381</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>848</v>
@@ -35469,16 +35469,16 @@
     </row>
     <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1381</v>
+        <v>1326</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>848</v>
+        <v>1333</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>420</v>
@@ -35486,16 +35486,16 @@
     </row>
     <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1326</v>
+        <v>1298</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>420</v>
@@ -35503,7 +35503,7 @@
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>1405</v>
@@ -35512,7 +35512,7 @@
         <v>1298</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>848</v>
+        <v>342</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>420</v>
@@ -35520,16 +35520,16 @@
     </row>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>1298</v>
+        <v>1309</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>342</v>
+        <v>848</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>420</v>
@@ -35537,13 +35537,13 @@
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>848</v>
@@ -35554,13 +35554,13 @@
     </row>
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>848</v>
@@ -35571,13 +35571,13 @@
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>1342</v>
+        <v>1424</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>848</v>
@@ -35588,13 +35588,13 @@
     </row>
     <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1424</v>
+        <v>1309</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>848</v>
@@ -35605,13 +35605,13 @@
     </row>
     <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>848</v>
@@ -35622,13 +35622,13 @@
     </row>
     <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>848</v>
@@ -35639,13 +35639,13 @@
     </row>
     <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1318</v>
+        <v>1339</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>848</v>
@@ -35656,13 +35656,13 @@
     </row>
     <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>1339</v>
+        <v>1330</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>848</v>
@@ -35673,13 +35673,13 @@
     </row>
     <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1330</v>
+        <v>1365</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>848</v>
@@ -35690,16 +35690,16 @@
     </row>
     <row r="94" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>1405</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1365</v>
+        <v>1296</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>848</v>
+        <v>985</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>420</v>
@@ -35707,30 +35707,28 @@
     </row>
     <row r="95" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1405</v>
+        <v>1433</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1296</v>
+        <v>1314</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>278</v>
@@ -35739,45 +35737,45 @@
     </row>
     <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E97" s="2"/>
+      <c r="E97" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1300</v>
+        <v>1389</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1389</v>
+        <v>1336</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>278</v>
@@ -35786,13 +35784,13 @@
     </row>
     <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1336</v>
+        <v>1298</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>278</v>
@@ -35801,13 +35799,13 @@
     </row>
     <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1298</v>
+        <v>1440</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>278</v>
@@ -35816,13 +35814,13 @@
     </row>
     <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1440</v>
+        <v>1314</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>278</v>
@@ -35831,13 +35829,13 @@
     </row>
     <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>1433</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1314</v>
+        <v>1443</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>278</v>
@@ -35846,28 +35844,28 @@
     </row>
     <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1443</v>
+        <v>1320</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>278</v>
+        <v>848</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>1445</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1320</v>
+        <v>1298</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>848</v>
@@ -35876,13 +35874,13 @@
     </row>
     <row r="106" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>1445</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1298</v>
+        <v>1448</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>848</v>
@@ -35891,45 +35889,45 @@
     </row>
     <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>1445</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1448</v>
+        <v>1389</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>1445</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1389</v>
+        <v>1314</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>1445</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1314</v>
+        <v>1389</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>848</v>
@@ -35938,13 +35936,13 @@
     </row>
     <row r="110" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>1445</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1389</v>
+        <v>1326</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>848</v>
@@ -35953,7 +35951,7 @@
     </row>
     <row r="111" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>1445</v>
@@ -35968,13 +35966,13 @@
     </row>
     <row r="112" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1326</v>
+        <v>1296</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>848</v>
@@ -35983,13 +35981,13 @@
     </row>
     <row r="113" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1296</v>
+        <v>1342</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>848</v>
@@ -35998,13 +35996,13 @@
     </row>
     <row r="114" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1342</v>
+        <v>1328</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>848</v>
@@ -36013,13 +36011,13 @@
     </row>
     <row r="115" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1328</v>
+        <v>1459</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>848</v>
@@ -36028,13 +36026,13 @@
     </row>
     <row r="116" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1459</v>
+        <v>1300</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>848</v>
@@ -36043,13 +36041,13 @@
     </row>
     <row r="117" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1300</v>
+        <v>1462</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>848</v>
@@ -36058,13 +36056,13 @@
     </row>
     <row r="118" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1462</v>
+        <v>1402</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>848</v>
@@ -36073,13 +36071,13 @@
     </row>
     <row r="119" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1402</v>
+        <v>1318</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>848</v>
@@ -36088,13 +36086,13 @@
     </row>
     <row r="120" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>1455</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>848</v>
@@ -36103,13 +36101,13 @@
     </row>
     <row r="121" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1455</v>
+        <v>1467</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1314</v>
+        <v>1395</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>848</v>
@@ -36118,28 +36116,30 @@
     </row>
     <row r="122" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1395</v>
+        <v>1371</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E122" s="2"/>
+      <c r="E122" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1371</v>
+        <v>1361</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>848</v>
@@ -36150,13 +36150,13 @@
     </row>
     <row r="124" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1361</v>
+        <v>1305</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>848</v>
@@ -36167,13 +36167,13 @@
     </row>
     <row r="125" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>848</v>
@@ -36184,30 +36184,28 @@
     </row>
     <row r="126" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>1307</v>
+        <v>764</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>764</v>
+        <v>1336</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>848</v>
@@ -36216,13 +36214,13 @@
     </row>
     <row r="128" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1336</v>
+        <v>1300</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>848</v>
@@ -36231,13 +36229,13 @@
     </row>
     <row r="129" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>1300</v>
+        <v>1361</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>848</v>
@@ -36246,13 +36244,13 @@
     </row>
     <row r="130" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1361</v>
+        <v>1477</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>848</v>
@@ -36261,13 +36259,13 @@
     </row>
     <row r="131" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>1477</v>
+        <v>1402</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>848</v>
@@ -36276,13 +36274,13 @@
     </row>
     <row r="132" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>1467</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1402</v>
+        <v>1309</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>848</v>
@@ -36291,13 +36289,13 @@
     </row>
     <row r="133" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1467</v>
+        <v>1481</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>848</v>
@@ -36306,13 +36304,13 @@
     </row>
     <row r="134" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>1481</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1314</v>
+        <v>1305</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>848</v>
@@ -36321,13 +36319,13 @@
     </row>
     <row r="135" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>1481</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>848</v>
@@ -36336,13 +36334,13 @@
     </row>
     <row r="136" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>848</v>
@@ -36351,13 +36349,13 @@
     </row>
     <row r="137" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1314</v>
+        <v>1336</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>848</v>
@@ -36366,13 +36364,13 @@
     </row>
     <row r="138" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1336</v>
+        <v>1381</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>848</v>
@@ -36381,13 +36379,13 @@
     </row>
     <row r="139" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1381</v>
+        <v>1489</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>848</v>
@@ -36396,13 +36394,13 @@
     </row>
     <row r="140" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1489</v>
+        <v>1402</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>848</v>
@@ -36411,13 +36409,13 @@
     </row>
     <row r="141" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1402</v>
+        <v>1303</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>848</v>
@@ -36426,13 +36424,13 @@
     </row>
     <row r="142" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1303</v>
+        <v>1462</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>848</v>
@@ -36441,13 +36439,13 @@
     </row>
     <row r="143" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1462</v>
+        <v>1320</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>848</v>
@@ -36456,13 +36454,13 @@
     </row>
     <row r="144" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>848</v>
@@ -36471,43 +36469,43 @@
     </row>
     <row r="145" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>848</v>
+        <v>1346</v>
       </c>
       <c r="E145" s="2"/>
     </row>
     <row r="146" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1309</v>
+        <v>1477</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1346</v>
+        <v>848</v>
       </c>
       <c r="E146" s="2"/>
     </row>
     <row r="147" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1477</v>
+        <v>1376</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>848</v>
@@ -36516,13 +36514,13 @@
     </row>
     <row r="148" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1376</v>
+        <v>1316</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>848</v>
@@ -36531,7 +36529,7 @@
     </row>
     <row r="149" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>1485</v>
@@ -36546,13 +36544,13 @@
     </row>
     <row r="150" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1316</v>
+        <v>1373</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>848</v>
@@ -36561,13 +36559,13 @@
     </row>
     <row r="151" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1373</v>
+        <v>792</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>848</v>
@@ -36576,45 +36574,45 @@
     </row>
     <row r="152" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>792</v>
+        <v>1440</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E152" s="2"/>
+      <c r="E152" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="153" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1440</v>
+        <v>1336</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E153" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E153" s="2"/>
     </row>
     <row r="154" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1336</v>
+        <v>1309</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>848</v>
@@ -36623,13 +36621,13 @@
     </row>
     <row r="155" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1309</v>
+        <v>1365</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>848</v>
@@ -36638,45 +36636,45 @@
     </row>
     <row r="156" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>1365</v>
+        <v>1339</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E156" s="2"/>
+      <c r="E156" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="157" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1339</v>
+        <v>1373</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E157" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E157" s="2"/>
     </row>
     <row r="158" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1373</v>
+        <v>1509</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>848</v>
@@ -36685,13 +36683,13 @@
     </row>
     <row r="159" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1509</v>
+        <v>1440</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>848</v>
@@ -36700,13 +36698,13 @@
     </row>
     <row r="160" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1440</v>
+        <v>1512</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>848</v>
@@ -36715,13 +36713,13 @@
     </row>
     <row r="161" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1512</v>
+        <v>1312</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>848</v>
@@ -36730,13 +36728,13 @@
     </row>
     <row r="162" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>848</v>
@@ -36745,13 +36743,13 @@
     </row>
     <row r="163" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1314</v>
+        <v>1509</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>848</v>
@@ -36760,13 +36758,13 @@
     </row>
     <row r="164" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1509</v>
+        <v>1402</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>848</v>
@@ -36775,13 +36773,13 @@
     </row>
     <row r="165" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1402</v>
+        <v>1361</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>848</v>
@@ -36790,13 +36788,13 @@
     </row>
     <row r="166" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1361</v>
+        <v>1519</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>848</v>
@@ -36805,13 +36803,13 @@
     </row>
     <row r="167" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1519</v>
+        <v>1316</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>848</v>
@@ -36820,13 +36818,13 @@
     </row>
     <row r="168" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>848</v>
@@ -36835,13 +36833,13 @@
     </row>
     <row r="169" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1322</v>
+        <v>1477</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>848</v>
@@ -36850,13 +36848,13 @@
     </row>
     <row r="170" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1477</v>
+        <v>1318</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>848</v>
@@ -36865,13 +36863,13 @@
     </row>
     <row r="171" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1318</v>
+        <v>1298</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>848</v>
@@ -36880,13 +36878,13 @@
     </row>
     <row r="172" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>848</v>
@@ -36895,13 +36893,13 @@
     </row>
     <row r="173" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>1485</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1305</v>
+        <v>1527</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>848</v>
@@ -36910,13 +36908,13 @@
     </row>
     <row r="174" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1485</v>
+        <v>1529</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1527</v>
+        <v>1307</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>848</v>
@@ -36925,13 +36923,13 @@
     </row>
     <row r="175" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>848</v>
@@ -36940,13 +36938,13 @@
     </row>
     <row r="176" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>848</v>
@@ -36955,45 +36953,45 @@
     </row>
     <row r="177" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1318</v>
+        <v>1533</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E177" s="2"/>
+      <c r="E177" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="178" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1533</v>
+        <v>1326</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E178" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E178" s="2"/>
     </row>
     <row r="179" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1326</v>
+        <v>1305</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>848</v>
@@ -37002,13 +37000,13 @@
     </row>
     <row r="180" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1305</v>
+        <v>1296</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>848</v>
@@ -37017,13 +37015,13 @@
     </row>
     <row r="181" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1296</v>
+        <v>1320</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>848</v>
@@ -37032,13 +37030,13 @@
     </row>
     <row r="182" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1320</v>
+        <v>1336</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>848</v>
@@ -37047,13 +37045,13 @@
     </row>
     <row r="183" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1336</v>
+        <v>1365</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>848</v>
@@ -37062,13 +37060,13 @@
     </row>
     <row r="184" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1365</v>
+        <v>1389</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>848</v>
@@ -37077,13 +37075,13 @@
     </row>
     <row r="185" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>1529</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>848</v>
@@ -37092,13 +37090,13 @@
     </row>
     <row r="186" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1529</v>
+        <v>1543</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1387</v>
+        <v>1544</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>848</v>
@@ -37107,28 +37105,30 @@
     </row>
     <row r="187" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1544</v>
+        <v>1381</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E187" s="2"/>
+      <c r="E187" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="188" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1381</v>
+        <v>1318</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>848</v>
@@ -37139,45 +37139,45 @@
     </row>
     <row r="189" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1318</v>
+        <v>1309</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E189" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E189" s="2"/>
     </row>
     <row r="190" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1309</v>
+        <v>1336</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E190" s="2"/>
+      <c r="E190" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="191" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1336</v>
+        <v>1550</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>848</v>
@@ -37188,30 +37188,28 @@
     </row>
     <row r="192" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1550</v>
+        <v>1402</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E192" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E192" s="2"/>
     </row>
     <row r="193" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>1543</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1402</v>
+        <v>1553</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>848</v>
@@ -37220,13 +37218,13 @@
     </row>
     <row r="194" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1543</v>
+        <v>1555</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>848</v>
@@ -37235,13 +37233,13 @@
     </row>
     <row r="195" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>1555</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>848</v>
@@ -37250,43 +37248,43 @@
     </row>
     <row r="196" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>1555</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1558</v>
+        <v>1477</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>848</v>
+        <v>1560</v>
       </c>
       <c r="E196" s="2"/>
     </row>
     <row r="197" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>1555</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1477</v>
+        <v>1330</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1560</v>
+        <v>848</v>
       </c>
       <c r="E197" s="2"/>
     </row>
     <row r="198" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>1555</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1330</v>
+        <v>1563</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>848</v>
@@ -37295,43 +37293,45 @@
     </row>
     <row r="199" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>1555</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1563</v>
+        <v>1328</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="E199" s="2"/>
     </row>
     <row r="200" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1555</v>
+        <v>1566</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>1328</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="E200" s="2"/>
+        <v>848</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="201" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>1566</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1328</v>
+        <v>1314</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>848</v>
@@ -37342,13 +37342,13 @@
     </row>
     <row r="202" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>1566</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1314</v>
+        <v>1387</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>848</v>
@@ -37359,13 +37359,13 @@
     </row>
     <row r="203" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>1566</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>848</v>
@@ -37376,30 +37376,30 @@
     </row>
     <row r="204" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1365</v>
+        <v>1572</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>848</v>
+        <v>1346</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>1346</v>
@@ -37410,13 +37410,13 @@
     </row>
     <row r="206" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>1346</v>
@@ -37427,13 +37427,13 @@
     </row>
     <row r="207" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>1576</v>
+        <v>1318</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>1346</v>
@@ -37444,7 +37444,7 @@
     </row>
     <row r="208" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>1571</v>
@@ -37461,13 +37461,13 @@
     </row>
     <row r="209" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>1318</v>
+        <v>1580</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>1346</v>
@@ -37478,13 +37478,13 @@
     </row>
     <row r="210" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1580</v>
+        <v>1322</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>1346</v>
@@ -37495,13 +37495,13 @@
     </row>
     <row r="211" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>1322</v>
+        <v>1361</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>1346</v>
@@ -37512,13 +37512,13 @@
     </row>
     <row r="212" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>1361</v>
+        <v>1342</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>1346</v>
@@ -37529,13 +37529,13 @@
     </row>
     <row r="213" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>1342</v>
+        <v>1314</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>1346</v>
@@ -37546,13 +37546,13 @@
     </row>
     <row r="214" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>1346</v>
@@ -37563,13 +37563,13 @@
     </row>
     <row r="215" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1320</v>
+        <v>1339</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>1346</v>
@@ -37580,13 +37580,13 @@
     </row>
     <row r="216" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1339</v>
+        <v>1307</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>1346</v>
@@ -37597,13 +37597,13 @@
     </row>
     <row r="217" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>1307</v>
+        <v>1558</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>1346</v>
@@ -37614,13 +37614,13 @@
     </row>
     <row r="218" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1558</v>
+        <v>1590</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>1346</v>
@@ -37631,13 +37631,13 @@
     </row>
     <row r="219" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>1571</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>1346</v>
@@ -37648,30 +37648,30 @@
     </row>
     <row r="220" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>1571</v>
+        <v>1594</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1592</v>
+        <v>1342</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>1346</v>
+        <v>848</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1342</v>
+        <v>1307</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>848</v>
@@ -37682,13 +37682,13 @@
     </row>
     <row r="222" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>1307</v>
+        <v>1597</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>848</v>
@@ -37699,13 +37699,13 @@
     </row>
     <row r="223" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>1597</v>
+        <v>1293</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>848</v>
@@ -37716,13 +37716,13 @@
     </row>
     <row r="224" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>1599</v>
+        <v>1330</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>848</v>
@@ -37733,13 +37733,13 @@
     </row>
     <row r="225" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>1330</v>
+        <v>1309</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>848</v>
@@ -37750,13 +37750,13 @@
     </row>
     <row r="226" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>1309</v>
+        <v>1603</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>848</v>
@@ -37767,13 +37767,13 @@
     </row>
     <row r="227" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>1594</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>1603</v>
+        <v>1314</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>848</v>
@@ -37784,30 +37784,28 @@
     </row>
     <row r="228" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>1594</v>
+        <v>1606</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E228" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E228" s="2"/>
     </row>
     <row r="229" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>1318</v>
+        <v>1477</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>848</v>
@@ -37816,13 +37814,13 @@
     </row>
     <row r="230" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1477</v>
+        <v>1314</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>848</v>
@@ -37831,13 +37829,13 @@
     </row>
     <row r="231" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>848</v>
@@ -37846,13 +37844,13 @@
     </row>
     <row r="232" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1316</v>
+        <v>1611</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>848</v>
@@ -37861,13 +37859,13 @@
     </row>
     <row r="233" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1611</v>
+        <v>792</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>848</v>
@@ -37876,13 +37874,13 @@
     </row>
     <row r="234" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>792</v>
+        <v>1558</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>848</v>
@@ -37891,13 +37889,13 @@
     </row>
     <row r="235" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1558</v>
+        <v>764</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>848</v>
@@ -37906,43 +37904,43 @@
     </row>
     <row r="236" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>764</v>
+        <v>1326</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>848</v>
+        <v>1333</v>
       </c>
       <c r="E236" s="2"/>
     </row>
     <row r="237" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1326</v>
+        <v>1617</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E237" s="2"/>
     </row>
     <row r="238" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>1617</v>
+        <v>792</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>848</v>
@@ -37951,45 +37949,45 @@
     </row>
     <row r="239" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>792</v>
+        <v>1402</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E239" s="2"/>
+      <c r="E239" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="240" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>1402</v>
+        <v>1387</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E240" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E240" s="2"/>
     </row>
     <row r="241" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>1387</v>
+        <v>1320</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>848</v>
@@ -37998,13 +37996,13 @@
     </row>
     <row r="242" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1320</v>
+        <v>1580</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>848</v>
@@ -38013,43 +38011,43 @@
     </row>
     <row r="243" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>1580</v>
+        <v>1298</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>848</v>
+        <v>1333</v>
       </c>
       <c r="E243" s="2"/>
     </row>
     <row r="244" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E244" s="2"/>
     </row>
     <row r="245" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>1305</v>
+        <v>1626</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>848</v>
@@ -38058,13 +38056,13 @@
     </row>
     <row r="246" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>1626</v>
+        <v>1389</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>848</v>
@@ -38073,13 +38071,13 @@
     </row>
     <row r="247" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>1389</v>
+        <v>1553</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>848</v>
@@ -38088,13 +38086,13 @@
     </row>
     <row r="248" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>1553</v>
+        <v>1630</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>848</v>
@@ -38103,75 +38101,75 @@
     </row>
     <row r="249" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>1630</v>
+        <v>1307</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E249" s="2"/>
+      <c r="E249" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="250" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>1307</v>
+        <v>1342</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E250" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E250" s="2"/>
     </row>
     <row r="251" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>1342</v>
+        <v>1519</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>848</v>
+        <v>1333</v>
       </c>
       <c r="E251" s="2"/>
     </row>
     <row r="252" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>1519</v>
+        <v>1635</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E252" s="2"/>
     </row>
     <row r="253" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>1635</v>
+        <v>1328</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>848</v>
@@ -38180,13 +38178,13 @@
     </row>
     <row r="254" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>1606</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>1328</v>
+        <v>1533</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>848</v>
@@ -38195,13 +38193,13 @@
     </row>
     <row r="255" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>1606</v>
+        <v>1639</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1533</v>
+        <v>1519</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>848</v>
@@ -38210,13 +38208,13 @@
     </row>
     <row r="256" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>1519</v>
+        <v>1533</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>848</v>
@@ -38225,13 +38223,13 @@
     </row>
     <row r="257" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1533</v>
+        <v>1303</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>848</v>
@@ -38240,13 +38238,13 @@
     </row>
     <row r="258" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1303</v>
+        <v>1318</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>848</v>
@@ -38255,7 +38253,7 @@
     </row>
     <row r="259" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>1639</v>
@@ -38266,17 +38264,19 @@
       <c r="D259" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E259" s="2"/>
+      <c r="E259" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="260" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>1318</v>
+        <v>1597</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>848</v>
@@ -38287,30 +38287,28 @@
     </row>
     <row r="261" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>1597</v>
+        <v>1330</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E261" s="2"/>
     </row>
     <row r="262" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>1330</v>
+        <v>1558</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>848</v>
@@ -38319,13 +38317,13 @@
     </row>
     <row r="263" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>1558</v>
+        <v>1371</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>848</v>
@@ -38334,13 +38332,13 @@
     </row>
     <row r="264" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>1371</v>
+        <v>1576</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>848</v>
@@ -38349,31 +38347,33 @@
     </row>
     <row r="265" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>1639</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>1576</v>
+        <v>1336</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E265" s="2"/>
+      <c r="E265" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="266" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>1639</v>
+        <v>1651</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>1336</v>
+        <v>1652</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>848</v>
+        <v>1653</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>420</v>
@@ -38381,13 +38381,13 @@
     </row>
     <row r="267" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>1651</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>1653</v>
@@ -38398,13 +38398,13 @@
     </row>
     <row r="268" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>1651</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>1655</v>
+        <v>1296</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>1653</v>
@@ -38415,30 +38415,28 @@
     </row>
     <row r="269" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>1651</v>
+        <v>1658</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>1296</v>
+        <v>1326</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E269" s="2"/>
     </row>
     <row r="270" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>1326</v>
+        <v>1305</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>848</v>
@@ -38447,13 +38445,13 @@
     </row>
     <row r="271" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>1305</v>
+        <v>1322</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>848</v>
@@ -38462,28 +38460,30 @@
     </row>
     <row r="272" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E272" s="2"/>
+      <c r="E272" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="273" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>848</v>
@@ -38494,30 +38494,28 @@
     </row>
     <row r="274" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>1312</v>
+        <v>1664</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E274" s="2"/>
     </row>
     <row r="275" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>1664</v>
+        <v>1320</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>848</v>
@@ -38526,13 +38524,13 @@
     </row>
     <row r="276" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>1658</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>1320</v>
+        <v>1667</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>848</v>
@@ -38541,13 +38539,13 @@
     </row>
     <row r="277" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>1658</v>
+        <v>1669</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>1667</v>
+        <v>1300</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>848</v>
@@ -38556,13 +38554,13 @@
     </row>
     <row r="278" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>1300</v>
+        <v>1336</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>848</v>
@@ -38571,13 +38569,13 @@
     </row>
     <row r="279" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>1336</v>
+        <v>1672</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>848</v>
@@ -38586,13 +38584,13 @@
     </row>
     <row r="280" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>1672</v>
+        <v>1381</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>848</v>
@@ -38601,31 +38599,33 @@
     </row>
     <row r="281" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>1381</v>
+        <v>1590</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E281" s="2"/>
+      <c r="E281" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="282" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>1590</v>
+        <v>1300</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>848</v>
+        <v>1560</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>420</v>
@@ -38633,30 +38633,28 @@
     </row>
     <row r="283" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>1300</v>
+        <v>1558</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>1560</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E283" s="2"/>
     </row>
     <row r="284" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>1558</v>
+        <v>1318</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>848</v>
@@ -38665,13 +38663,13 @@
     </row>
     <row r="285" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>1318</v>
+        <v>1389</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>848</v>
@@ -38680,45 +38678,45 @@
     </row>
     <row r="286" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>1389</v>
+        <v>1318</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E286" s="2"/>
+      <c r="E286" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="287" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>1318</v>
+        <v>1402</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E287" s="2"/>
     </row>
     <row r="288" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>1402</v>
+        <v>1664</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>848</v>
@@ -38727,13 +38725,13 @@
     </row>
     <row r="289" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>1664</v>
+        <v>1683</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>848</v>
@@ -38742,13 +38740,13 @@
     </row>
     <row r="290" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>1683</v>
+        <v>1296</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>848</v>
@@ -38757,13 +38755,13 @@
     </row>
     <row r="291" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>1296</v>
+        <v>1389</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>848</v>
@@ -38772,45 +38770,45 @@
     </row>
     <row r="292" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>1389</v>
+        <v>1687</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="E292" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="293" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E293" s="2"/>
     </row>
     <row r="294" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>1689</v>
+        <v>1316</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>848</v>
@@ -38819,13 +38817,13 @@
     </row>
     <row r="295" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>1316</v>
+        <v>1336</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>848</v>
@@ -38834,43 +38832,43 @@
     </row>
     <row r="296" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>848</v>
+        <v>1118</v>
       </c>
       <c r="E296" s="2"/>
     </row>
     <row r="297" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>1318</v>
+        <v>1694</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>1118</v>
+        <v>848</v>
       </c>
       <c r="E297" s="2"/>
     </row>
     <row r="298" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>1694</v>
+        <v>1305</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>848</v>
@@ -38879,13 +38877,13 @@
     </row>
     <row r="299" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>1305</v>
+        <v>1697</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>848</v>
@@ -38894,13 +38892,13 @@
     </row>
     <row r="300" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>1697</v>
+        <v>1544</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>848</v>
@@ -38909,13 +38907,13 @@
     </row>
     <row r="301" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>1544</v>
+        <v>1462</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>848</v>
@@ -38924,43 +38922,43 @@
     </row>
     <row r="302" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>1462</v>
+        <v>1314</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>848</v>
+        <v>1346</v>
       </c>
       <c r="E302" s="2"/>
     </row>
     <row r="303" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>1314</v>
+        <v>1702</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>1346</v>
+        <v>848</v>
       </c>
       <c r="E303" s="2"/>
     </row>
     <row r="304" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>1702</v>
+        <v>1300</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>848</v>
@@ -38969,13 +38967,13 @@
     </row>
     <row r="305" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>1300</v>
+        <v>1705</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>848</v>
@@ -38984,45 +38982,45 @@
     </row>
     <row r="306" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>1705</v>
+        <v>1336</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E306" s="2"/>
+      <c r="E306" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="307" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>1336</v>
+        <v>1553</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E307" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E307" s="2"/>
     </row>
     <row r="308" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>1553</v>
+        <v>1342</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>848</v>
@@ -39031,13 +39029,13 @@
     </row>
     <row r="309" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>1342</v>
+        <v>1635</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>848</v>
@@ -39046,13 +39044,13 @@
     </row>
     <row r="310" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>1635</v>
+        <v>1307</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>848</v>
@@ -39061,13 +39059,13 @@
     </row>
     <row r="311" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>1307</v>
+        <v>1316</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>848</v>
@@ -39076,13 +39074,13 @@
     </row>
     <row r="312" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>1316</v>
+        <v>1580</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>848</v>
@@ -39091,13 +39089,13 @@
     </row>
     <row r="313" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1580</v>
+        <v>1714</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>848</v>
@@ -39106,13 +39104,13 @@
     </row>
     <row r="314" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1714</v>
+        <v>1328</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>848</v>
@@ -39121,13 +39119,13 @@
     </row>
     <row r="315" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>1328</v>
+        <v>1603</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>848</v>
@@ -39136,13 +39134,13 @@
     </row>
     <row r="316" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>1603</v>
+        <v>1556</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>848</v>
@@ -39151,13 +39149,13 @@
     </row>
     <row r="317" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>1556</v>
+        <v>1440</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>848</v>
@@ -39166,13 +39164,13 @@
     </row>
     <row r="318" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1440</v>
+        <v>1687</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>848</v>
@@ -39181,13 +39179,13 @@
     </row>
     <row r="319" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1687</v>
+        <v>1300</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>848</v>
@@ -39196,45 +39194,45 @@
     </row>
     <row r="320" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>1300</v>
+        <v>1314</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E320" s="2"/>
+      <c r="E320" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="321" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>1314</v>
+        <v>1371</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E321" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E321" s="2"/>
     </row>
     <row r="322" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>1371</v>
+        <v>1309</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>848</v>
@@ -39243,13 +39241,13 @@
     </row>
     <row r="323" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>848</v>
@@ -39258,13 +39256,13 @@
     </row>
     <row r="324" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>1318</v>
+        <v>1635</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>848</v>
@@ -39273,13 +39271,13 @@
     </row>
     <row r="325" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>1635</v>
+        <v>1462</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>848</v>
@@ -39288,45 +39286,45 @@
     </row>
     <row r="326" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>1462</v>
+        <v>1728</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="E326" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="327" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>1728</v>
+        <v>1389</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="E327" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="E327" s="2"/>
     </row>
     <row r="328" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>1389</v>
+        <v>1318</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>848</v>
@@ -39335,13 +39333,13 @@
     </row>
     <row r="329" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>1318</v>
+        <v>1307</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>848</v>
@@ -39350,13 +39348,13 @@
     </row>
     <row r="330" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1307</v>
+        <v>1630</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>848</v>
@@ -39365,13 +39363,13 @@
     </row>
     <row r="331" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>1630</v>
+        <v>1402</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>848</v>
@@ -39380,13 +39378,13 @@
     </row>
     <row r="332" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>1402</v>
+        <v>1314</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>848</v>
@@ -39395,13 +39393,13 @@
     </row>
     <row r="333" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>848</v>
@@ -39410,13 +39408,13 @@
     </row>
     <row r="334" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>1298</v>
+        <v>1737</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>848</v>
@@ -39425,28 +39423,30 @@
     </row>
     <row r="335" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>1737</v>
+        <v>1714</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E335" s="2"/>
+      <c r="E335" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="336" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>1714</v>
+        <v>1414</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>848</v>
@@ -39457,45 +39457,45 @@
     </row>
     <row r="337" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>1414</v>
+        <v>1300</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E337" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E337" s="2"/>
     </row>
     <row r="338" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1300</v>
+        <v>1336</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E338" s="2"/>
+      <c r="E338" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="339" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>1336</v>
+        <v>1402</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>848</v>
@@ -39506,30 +39506,28 @@
     </row>
     <row r="340" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>1402</v>
+        <v>1489</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E340" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E340" s="2"/>
     </row>
     <row r="341" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>1489</v>
+        <v>1312</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>848</v>
@@ -39538,28 +39536,30 @@
     </row>
     <row r="342" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E342" s="2"/>
+      <c r="E342" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="343" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>1318</v>
+        <v>1576</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>848</v>
@@ -39570,30 +39570,28 @@
     </row>
     <row r="344" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>1576</v>
+        <v>1748</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E344" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E344" s="2"/>
     </row>
     <row r="345" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>848</v>
@@ -39602,13 +39600,13 @@
     </row>
     <row r="346" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>1750</v>
+        <v>1597</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>848</v>
@@ -39617,45 +39615,45 @@
     </row>
     <row r="347" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1597</v>
+        <v>1462</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E347" s="2"/>
+      <c r="E347" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="348" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>1462</v>
+        <v>1314</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E348" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E348" s="2"/>
     </row>
     <row r="349" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>1314</v>
+        <v>1387</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>848</v>
@@ -39664,28 +39662,30 @@
     </row>
     <row r="350" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>1669</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E350" s="2"/>
+      <c r="E350" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="351" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>1669</v>
+        <v>1757</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>1361</v>
+        <v>1326</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>848</v>
@@ -39696,13 +39696,13 @@
     </row>
     <row r="352" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>848</v>
@@ -39713,13 +39713,13 @@
     </row>
     <row r="353" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1339</v>
+        <v>1318</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>848</v>
@@ -39730,13 +39730,13 @@
     </row>
     <row r="354" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1318</v>
+        <v>1296</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>848</v>
@@ -39747,13 +39747,13 @@
     </row>
     <row r="355" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1296</v>
+        <v>1694</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>848</v>
@@ -39764,13 +39764,13 @@
     </row>
     <row r="356" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1694</v>
+        <v>1381</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>848</v>
@@ -39781,16 +39781,16 @@
     </row>
     <row r="357" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1381</v>
+        <v>1519</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>848</v>
+        <v>1560</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>420</v>
@@ -39798,16 +39798,16 @@
     </row>
     <row r="358" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1519</v>
+        <v>1314</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>1560</v>
+        <v>848</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>420</v>
@@ -39815,13 +39815,13 @@
     </row>
     <row r="359" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1314</v>
+        <v>1395</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>848</v>
@@ -39832,13 +39832,13 @@
     </row>
     <row r="360" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1395</v>
+        <v>1574</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>848</v>
@@ -39849,13 +39849,13 @@
     </row>
     <row r="361" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1574</v>
+        <v>1336</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>848</v>
@@ -39866,13 +39866,13 @@
     </row>
     <row r="362" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1336</v>
+        <v>1402</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>848</v>
@@ -39883,13 +39883,13 @@
     </row>
     <row r="363" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1402</v>
+        <v>1336</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>848</v>
@@ -39900,13 +39900,13 @@
     </row>
     <row r="364" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1336</v>
+        <v>1395</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>848</v>
@@ -39917,13 +39917,13 @@
     </row>
     <row r="365" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>1757</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1395</v>
+        <v>1318</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>848</v>
@@ -39934,13 +39934,13 @@
     </row>
     <row r="366" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>1757</v>
+        <v>1773</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1318</v>
+        <v>1296</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>848</v>
@@ -39951,144 +39951,142 @@
     </row>
     <row r="367" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E367" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E367" s="2"/>
     </row>
     <row r="368" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1303</v>
+        <v>1556</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>848</v>
+        <v>249</v>
       </c>
       <c r="E368" s="2"/>
     </row>
     <row r="369" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1556</v>
+        <v>1664</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="E369" s="2"/>
     </row>
     <row r="370" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1664</v>
+        <v>1778</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>278</v>
+        <v>848</v>
       </c>
       <c r="E370" s="2"/>
     </row>
     <row r="371" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1778</v>
+        <v>1318</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>848</v>
+        <v>545</v>
       </c>
       <c r="E371" s="2"/>
     </row>
     <row r="372" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1318</v>
+        <v>1558</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>545</v>
+        <v>848</v>
       </c>
       <c r="E372" s="2"/>
     </row>
     <row r="373" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1558</v>
+        <v>1402</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>848</v>
+        <v>418</v>
       </c>
       <c r="E373" s="2"/>
     </row>
     <row r="374" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>1781</v>
+        <v>2227</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1402</v>
+        <v>1309</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>418</v>
+        <v>2203</v>
       </c>
       <c r="E374" s="2"/>
     </row>
     <row r="375" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>2227</v>
+        <v>1782</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1309</v>
+        <v>1389</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>2203</v>
+        <v>545</v>
       </c>
       <c r="E375" s="2"/>
     </row>
     <row r="376" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>1773</v>
@@ -40097,94 +40095,94 @@
         <v>1389</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>545</v>
+        <v>1333</v>
       </c>
       <c r="E376" s="2"/>
     </row>
     <row r="377" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1389</v>
+        <v>1316</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E377" s="2"/>
     </row>
     <row r="378" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>1316</v>
+        <v>1296</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>848</v>
+        <v>418</v>
       </c>
       <c r="E378" s="2"/>
     </row>
     <row r="379" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>418</v>
+        <v>249</v>
       </c>
       <c r="E379" s="2"/>
     </row>
     <row r="380" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1305</v>
+        <v>1512</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>249</v>
+        <v>545</v>
       </c>
       <c r="E380" s="2"/>
     </row>
     <row r="381" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1512</v>
+        <v>1635</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>545</v>
+        <v>848</v>
       </c>
       <c r="E381" s="2"/>
     </row>
     <row r="382" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1635</v>
+        <v>1326</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>848</v>
@@ -40193,238 +40191,238 @@
     </row>
     <row r="383" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
-        <v>1789</v>
+        <v>2170</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1326</v>
+        <v>1307</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>848</v>
+        <v>2166</v>
       </c>
       <c r="E383" s="2"/>
     </row>
     <row r="384" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
-        <v>2170</v>
+        <v>1790</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>1307</v>
+        <v>1371</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>2166</v>
+        <v>848</v>
       </c>
       <c r="E384" s="2"/>
     </row>
     <row r="385" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1371</v>
+        <v>1298</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>848</v>
+        <v>278</v>
       </c>
       <c r="E385" s="2"/>
     </row>
     <row r="386" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
-        <v>1791</v>
+        <v>2226</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1298</v>
+        <v>1336</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>278</v>
+        <v>2203</v>
       </c>
       <c r="E386" s="2"/>
     </row>
     <row r="387" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
-        <v>2226</v>
+        <v>1792</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1336</v>
+        <v>1293</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>2203</v>
+        <v>418</v>
       </c>
       <c r="E387" s="2"/>
     </row>
     <row r="388" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1293</v>
+        <v>1365</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="E388" s="2"/>
     </row>
     <row r="389" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1365</v>
+        <v>1303</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>432</v>
+        <v>545</v>
       </c>
       <c r="E389" s="2"/>
     </row>
     <row r="390" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1303</v>
+        <v>1314</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>545</v>
+        <v>418</v>
       </c>
       <c r="E390" s="2"/>
     </row>
     <row r="391" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1314</v>
+        <v>1728</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>418</v>
+        <v>249</v>
       </c>
       <c r="E391" s="2"/>
     </row>
     <row r="392" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1728</v>
+        <v>1371</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>249</v>
+        <v>1333</v>
       </c>
       <c r="E392" s="2"/>
     </row>
     <row r="393" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>1371</v>
+        <v>1326</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1333</v>
+        <v>418</v>
       </c>
       <c r="E393" s="2"/>
     </row>
     <row r="394" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="E394" s="2"/>
     </row>
     <row r="395" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1318</v>
+        <v>1381</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="E395" s="2"/>
     </row>
     <row r="396" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1381</v>
+        <v>1303</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>418</v>
+        <v>1333</v>
       </c>
       <c r="E396" s="2"/>
     </row>
     <row r="397" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>1303</v>
+        <v>1424</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>1333</v>
+        <v>432</v>
       </c>
       <c r="E397" s="2"/>
     </row>
     <row r="398" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>1424</v>
+        <v>1489</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>432</v>
@@ -40433,73 +40431,73 @@
     </row>
     <row r="399" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1489</v>
+        <v>1296</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>432</v>
+        <v>249</v>
       </c>
       <c r="E399" s="2"/>
     </row>
     <row r="400" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1296</v>
+        <v>1318</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>249</v>
+        <v>418</v>
       </c>
       <c r="E400" s="2"/>
     </row>
     <row r="401" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>418</v>
+        <v>1333</v>
       </c>
       <c r="E401" s="2"/>
     </row>
     <row r="402" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>1314</v>
+        <v>1687</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E402" s="2"/>
     </row>
     <row r="403" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>1773</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>848</v>
@@ -40508,28 +40506,30 @@
     </row>
     <row r="404" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1773</v>
+        <v>1810</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1689</v>
+        <v>1328</v>
       </c>
       <c r="D404" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E404" s="2"/>
+      <c r="E404" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="405" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>1810</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>1328</v>
+        <v>1342</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>848</v>
@@ -40540,13 +40540,13 @@
     </row>
     <row r="406" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>1810</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1342</v>
+        <v>1305</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>848</v>
@@ -40557,13 +40557,13 @@
     </row>
     <row r="407" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>1810</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1305</v>
+        <v>1358</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>848</v>
@@ -40574,13 +40574,13 @@
     </row>
     <row r="408" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>1810</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1358</v>
+        <v>1307</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>848</v>
@@ -40591,13 +40591,13 @@
     </row>
     <row r="409" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>1810</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1307</v>
+        <v>1533</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>848</v>
@@ -40608,13 +40608,13 @@
     </row>
     <row r="410" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>1810</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1533</v>
+        <v>1373</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>848</v>
@@ -40625,13 +40625,13 @@
     </row>
     <row r="411" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1373</v>
+        <v>1318</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>848</v>
@@ -40642,13 +40642,13 @@
     </row>
     <row r="412" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>1818</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1318</v>
+        <v>1519</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>848</v>
@@ -40659,13 +40659,13 @@
     </row>
     <row r="413" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>1818</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1519</v>
+        <v>1305</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>848</v>
@@ -40676,13 +40676,13 @@
     </row>
     <row r="414" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>1818</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1305</v>
+        <v>1553</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>848</v>
@@ -40693,13 +40693,13 @@
     </row>
     <row r="415" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1553</v>
+        <v>1519</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>848</v>
@@ -40710,13 +40710,13 @@
     </row>
     <row r="416" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1519</v>
+        <v>1314</v>
       </c>
       <c r="D416" s="2" t="s">
         <v>848</v>
@@ -40727,13 +40727,13 @@
     </row>
     <row r="417" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>848</v>
@@ -40744,13 +40744,13 @@
     </row>
     <row r="418" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="D418" s="2" t="s">
         <v>848</v>
@@ -40761,13 +40761,13 @@
     </row>
     <row r="419" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1296</v>
+        <v>1553</v>
       </c>
       <c r="D419" s="2" t="s">
         <v>848</v>
@@ -40778,13 +40778,13 @@
     </row>
     <row r="420" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1553</v>
+        <v>1635</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>848</v>
@@ -40795,13 +40795,13 @@
     </row>
     <row r="421" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1635</v>
+        <v>1309</v>
       </c>
       <c r="D421" s="2" t="s">
         <v>848</v>
@@ -40812,13 +40812,13 @@
     </row>
     <row r="422" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1309</v>
+        <v>1300</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>848</v>
@@ -40829,13 +40829,13 @@
     </row>
     <row r="423" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1300</v>
+        <v>1832</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>848</v>
@@ -40846,13 +40846,13 @@
     </row>
     <row r="424" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1832</v>
+        <v>1330</v>
       </c>
       <c r="D424" s="2" t="s">
         <v>848</v>
@@ -40863,13 +40863,13 @@
     </row>
     <row r="425" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>848</v>
@@ -40880,13 +40880,13 @@
     </row>
     <row r="426" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1328</v>
+        <v>1590</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>848</v>
@@ -40897,13 +40897,13 @@
     </row>
     <row r="427" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>1823</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1590</v>
+        <v>1336</v>
       </c>
       <c r="D427" s="2" t="s">
         <v>848</v>
@@ -40914,30 +40914,28 @@
     </row>
     <row r="428" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1823</v>
+        <v>1838</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E428" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E428" s="2"/>
     </row>
     <row r="429" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>1838</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1328</v>
+        <v>1558</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>848</v>
@@ -40946,13 +40944,13 @@
     </row>
     <row r="430" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1558</v>
+        <v>1342</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>848</v>
@@ -40961,13 +40959,13 @@
     </row>
     <row r="431" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>1841</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1342</v>
+        <v>1843</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>848</v>
@@ -40976,13 +40974,13 @@
     </row>
     <row r="432" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>1841</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1843</v>
+        <v>1402</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>848</v>
@@ -40991,13 +40989,13 @@
     </row>
     <row r="433" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>1841</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1402</v>
+        <v>1307</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>848</v>
@@ -41006,13 +41004,13 @@
     </row>
     <row r="434" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>1841</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1307</v>
+        <v>1339</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>848</v>
@@ -41021,28 +41019,30 @@
     </row>
     <row r="435" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1841</v>
+        <v>1848</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1339</v>
+        <v>1330</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E435" s="2"/>
+      <c r="E435" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="436" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>1848</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>848</v>
@@ -41053,13 +41053,13 @@
     </row>
     <row r="437" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>1848</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>848</v>
@@ -41070,7 +41070,7 @@
     </row>
     <row r="438" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>1848</v>
@@ -41087,13 +41087,13 @@
     </row>
     <row r="439" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>1848</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>848</v>
@@ -41104,13 +41104,13 @@
     </row>
     <row r="440" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>1848</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1318</v>
+        <v>1371</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>848</v>
@@ -41121,13 +41121,13 @@
     </row>
     <row r="441" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>1848</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1371</v>
+        <v>1336</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>848</v>
@@ -41138,30 +41138,28 @@
     </row>
     <row r="442" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>1848</v>
+        <v>1856</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1336</v>
+        <v>1857</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E442" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E442" s="2"/>
     </row>
     <row r="443" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1857</v>
+        <v>1381</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>848</v>
@@ -41170,45 +41168,45 @@
     </row>
     <row r="444" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1381</v>
+        <v>1655</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E444" s="2"/>
+      <c r="E444" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="445" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1655</v>
+        <v>1861</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E445" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E445" s="2"/>
     </row>
     <row r="446" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>848</v>
@@ -41217,13 +41215,13 @@
     </row>
     <row r="447" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>848</v>
@@ -41232,13 +41230,13 @@
     </row>
     <row r="448" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1865</v>
+        <v>1314</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>848</v>
@@ -41247,13 +41245,13 @@
     </row>
     <row r="449" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1314</v>
+        <v>1778</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>848</v>
@@ -41262,45 +41260,45 @@
     </row>
     <row r="450" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1778</v>
+        <v>1326</v>
       </c>
       <c r="D450" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E450" s="2"/>
+      <c r="E450" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="451" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="D451" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E451" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E451" s="2"/>
     </row>
     <row r="452" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1318</v>
+        <v>792</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>848</v>
@@ -41309,13 +41307,13 @@
     </row>
     <row r="453" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>792</v>
+        <v>1872</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>848</v>
@@ -41324,13 +41322,13 @@
     </row>
     <row r="454" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1872</v>
+        <v>1635</v>
       </c>
       <c r="D454" s="2" t="s">
         <v>848</v>
@@ -41339,13 +41337,13 @@
     </row>
     <row r="455" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1635</v>
+        <v>1298</v>
       </c>
       <c r="D455" s="2" t="s">
         <v>848</v>
@@ -41354,13 +41352,13 @@
     </row>
     <row r="456" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1298</v>
+        <v>1857</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>848</v>
@@ -41369,13 +41367,13 @@
     </row>
     <row r="457" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1857</v>
+        <v>1877</v>
       </c>
       <c r="D457" s="2" t="s">
         <v>848</v>
@@ -41384,13 +41382,13 @@
     </row>
     <row r="458" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1877</v>
+        <v>1574</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>848</v>
@@ -41399,13 +41397,13 @@
     </row>
     <row r="459" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1574</v>
+        <v>1324</v>
       </c>
       <c r="D459" s="2" t="s">
         <v>848</v>
@@ -41414,13 +41412,13 @@
     </row>
     <row r="460" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="D460" s="2" t="s">
         <v>848</v>
@@ -41429,13 +41427,13 @@
     </row>
     <row r="461" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1336</v>
+        <v>1882</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>848</v>
@@ -41444,13 +41442,13 @@
     </row>
     <row r="462" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>1856</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1882</v>
+        <v>1533</v>
       </c>
       <c r="D462" s="2" t="s">
         <v>848</v>
@@ -41459,13 +41457,13 @@
     </row>
     <row r="463" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1856</v>
+        <v>1885</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1533</v>
+        <v>1314</v>
       </c>
       <c r="D463" s="2" t="s">
         <v>848</v>
@@ -41474,109 +41472,109 @@
     </row>
     <row r="464" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1314</v>
+        <v>1387</v>
       </c>
       <c r="D464" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E464" s="2"/>
+      <c r="E464" s="2" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="465" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1387</v>
+        <v>1336</v>
       </c>
       <c r="D465" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E465" s="2" t="s">
-        <v>390</v>
-      </c>
+      <c r="E465" s="2"/>
     </row>
     <row r="466" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1336</v>
+        <v>1889</v>
       </c>
       <c r="D466" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E466" s="2"/>
+      <c r="E466" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="467" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1889</v>
+        <v>1322</v>
       </c>
       <c r="D467" s="2" t="s">
         <v>848</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="468" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>1885</v>
       </c>
-      <c r="C468" s="2" t="s">
-        <v>1322</v>
-      </c>
+      <c r="C468" s="2"/>
       <c r="D468" s="2" t="s">
         <v>848</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
     </row>
     <row r="469" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>1885</v>
       </c>
-      <c r="C469" s="2"/>
+      <c r="C469" s="2" t="s">
+        <v>1580</v>
+      </c>
       <c r="D469" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E469" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="E469" s="2"/>
     </row>
     <row r="470" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1580</v>
+        <v>1300</v>
       </c>
       <c r="D470" s="2" t="s">
         <v>848</v>
@@ -41585,13 +41583,13 @@
     </row>
     <row r="471" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D471" s="2" t="s">
         <v>848</v>
@@ -41600,13 +41598,13 @@
     </row>
     <row r="472" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1298</v>
+        <v>1307</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>848</v>
@@ -41615,14 +41613,12 @@
     </row>
     <row r="473" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>1885</v>
       </c>
-      <c r="C473" s="2" t="s">
-        <v>1307</v>
-      </c>
+      <c r="C473" s="2"/>
       <c r="D473" s="2" t="s">
         <v>848</v>
       </c>
@@ -41630,12 +41626,14 @@
     </row>
     <row r="474" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>1885</v>
       </c>
-      <c r="C474" s="2"/>
+      <c r="C474" s="2" t="s">
+        <v>1664</v>
+      </c>
       <c r="D474" s="2" t="s">
         <v>848</v>
       </c>
@@ -41643,13 +41641,13 @@
     </row>
     <row r="475" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1664</v>
+        <v>1309</v>
       </c>
       <c r="D475" s="2" t="s">
         <v>848</v>
@@ -41658,14 +41656,12 @@
     </row>
     <row r="476" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C476" s="2" t="s">
-        <v>1309</v>
-      </c>
+        <v>1900</v>
+      </c>
+      <c r="C476" s="2"/>
       <c r="D476" s="2" t="s">
         <v>848</v>
       </c>
@@ -41673,12 +41669,14 @@
     </row>
     <row r="477" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C477" s="2"/>
+      <c r="C477" s="2" t="s">
+        <v>1728</v>
+      </c>
       <c r="D477" s="2" t="s">
         <v>848</v>
       </c>
@@ -41686,42 +41684,40 @@
     </row>
     <row r="478" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C478" s="2" t="s">
-        <v>1728</v>
-      </c>
+      <c r="C478" s="2"/>
       <c r="D478" s="2" t="s">
-        <v>848</v>
+        <v>1333</v>
       </c>
       <c r="E478" s="2"/>
     </row>
     <row r="479" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C479" s="2"/>
+      <c r="C479" s="2" t="s">
+        <v>1402</v>
+      </c>
       <c r="D479" s="2" t="s">
-        <v>1333</v>
+        <v>848</v>
       </c>
       <c r="E479" s="2"/>
     </row>
     <row r="480" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C480" s="2" t="s">
-        <v>1402</v>
-      </c>
+      <c r="C480" s="2"/>
       <c r="D480" s="2" t="s">
         <v>848</v>
       </c>
@@ -41729,7 +41725,7 @@
     </row>
     <row r="481" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>1900</v>
@@ -41742,12 +41738,14 @@
     </row>
     <row r="482" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C482" s="2"/>
+      <c r="C482" s="2" t="s">
+        <v>1298</v>
+      </c>
       <c r="D482" s="2" t="s">
         <v>848</v>
       </c>
@@ -41755,22 +41753,20 @@
     </row>
     <row r="483" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C483" s="2" t="s">
-        <v>1298</v>
-      </c>
+      <c r="C483" s="2"/>
       <c r="D483" s="2" t="s">
-        <v>848</v>
+        <v>1333</v>
       </c>
       <c r="E483" s="2"/>
     </row>
     <row r="484" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>1900</v>
@@ -41783,29 +41779,16 @@
     </row>
     <row r="485" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>1900</v>
       </c>
       <c r="C485" s="2"/>
       <c r="D485" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E485" s="2"/>
-    </row>
-    <row r="486" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A486" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B486" s="2" t="s">
-        <v>1900</v>
-      </c>
-      <c r="C486" s="2"/>
-      <c r="D486" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E486" s="2" t="s">
+      <c r="E485" s="2" t="s">
         <v>420</v>
       </c>
     </row>
